--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488171_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488171_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4178</v>
+        <v>7.2716</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0823</v>
+        <v>5.1577</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3355</v>
+        <v>2.1139</v>
       </c>
       <c r="G2" t="n">
         <v>3.2172</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>2.981</v>
+        <v>1.8348</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6266</v>
+        <v>0.702</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3544</v>
+        <v>1.1328</v>
       </c>
       <c r="V2" t="n">
         <v>3.146</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7676</v>
+        <v>4.719</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1532</v>
+        <v>4.0553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.6637</v>
       </c>
       <c r="G3" t="n">
         <v>2.8631</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1634</v>
+        <v>0.1147</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3246</v>
+        <v>0.2266</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1612</v>
+        <v>-0.1119</v>
       </c>
       <c r="V3" t="n">
         <v>0.6294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8256</v>
+        <v>1.9251</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0593</v>
+        <v>0.2326</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7664</v>
+        <v>1.6925</v>
       </c>
       <c r="G4" t="n">
         <v>0.4662</v>
@@ -766,13 +766,13 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1742</v>
+        <v>1.2737</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1379</v>
+        <v>0.3112</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0363</v>
+        <v>0.9625</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0486</v>
+        <v>1.7839</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1107</v>
+        <v>0.3406</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0621</v>
+        <v>1.4433</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7453</v>
+        <v>-0.1431</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4869</v>
+        <v>0.1271</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2322</v>
+        <v>-0.2702</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5775</v>
+        <v>0.976</v>
       </c>
       <c r="K5" t="n">
-        <v>2.28</v>
+        <v>0.8931</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7025</v>
+        <v>0.0829</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3228</v>
+        <v>-1.1191</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7931</v>
+        <v>-0.766</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.3531</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2226</v>
+        <v>0.291</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4079</v>
+        <v>0.2649</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4616</v>
+        <v>0.63</v>
       </c>
       <c r="W5" t="n">
-        <v>3.4616</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9457</v>
+        <v>1.4951</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4976</v>
+        <v>1.5572</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4433</v>
+        <v>-0.0621</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1431</v>
+        <v>-0.7453</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1271</v>
+        <v>0.4869</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2702</v>
+        <v>-1.2322</v>
       </c>
       <c r="J6" t="n">
-        <v>0.976</v>
+        <v>1.5775</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8931</v>
+        <v>2.28</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0829</v>
+        <v>-0.7025</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1191</v>
+        <v>-2.3228</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.766</v>
+        <v>-1.7931</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3531</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2823</v>
+        <v>0.6317</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5471</v>
+        <v>0.2239</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2649</v>
+        <v>0.4079</v>
       </c>
       <c r="V6" t="n">
-        <v>0.63</v>
+        <v>3.4616</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.4616</v>
       </c>
       <c r="X6" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9093</v>
+        <v>0.3221</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3459</v>
+        <v>0.3221</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4366</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4686</v>
+        <v>0.3221</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3026</v>
+        <v>0.3221</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8339</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.459</v>
+        <v>0.3221</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0704</v>
+        <v>0.3221</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009599999999999999</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2322</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2226</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1993</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8133</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3221</v>
+        <v>0.273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3221</v>
+        <v>1.6604</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-1.3873</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3221</v>
+        <v>2.4686</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3221</v>
+        <v>3.3026</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.8339</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3221</v>
+        <v>2.459</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3221</v>
+        <v>3.0704</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.2322</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.2226</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1278</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.4352</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4414</v>
+        <v>-0.2707</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0389</v>
+        <v>0.2549</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4025</v>
+        <v>-0.5256</v>
       </c>
       <c r="G9" t="n">
         <v>0.185</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0149</v>
+        <v>0.1558</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2736</v>
+        <v>0.0202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2586</v>
+        <v>0.1355</v>
       </c>
       <c r="V9" t="n">
         <v>0.315</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0984</v>
+        <v>-1.0497</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1535</v>
+        <v>-0.0555</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.945</v>
+        <v>-0.9942</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9153</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2393</v>
+        <v>-0.1906</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>-0.1756</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0343</v>
+        <v>-0.0149</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8547</v>
+        <v>-1.4378</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9488</v>
+        <v>-2.655</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0941</v>
+        <v>1.2172</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9116</v>
@@ -1312,13 +1312,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2761</v>
+        <v>0.1408</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7113</v>
+        <v>-0.4175</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4352</v>
+        <v>0.5583</v>
       </c>
       <c r="V11" t="n">
         <v>0.63</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8891</v>
+        <v>-1.8047</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3663</v>
+        <v>-1.5282</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5228</v>
+        <v>-0.2766</v>
       </c>
       <c r="G12" t="n">
         <v>-0.216</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5434</v>
+        <v>0.5409</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9849</v>
+        <v>-0.1467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4414</v>
+        <v>0.6877</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5738</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.9531</v>
+        <v>13.2269</v>
       </c>
       <c r="E13" t="n">
-        <v>9.0684</v>
+        <v>9.3421</v>
       </c>
       <c r="F13" t="n">
-        <v>3.884699999999999</v>
+        <v>3.884799999999999</v>
       </c>
       <c r="G13" t="n">
         <v>6.5909</v>
@@ -1468,19 +1468,19 @@
         <v>11.1173</v>
       </c>
       <c r="S13" t="n">
-        <v>5.347199999999999</v>
+        <v>5.620699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8892999999999996</v>
+        <v>1.1629</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4578</v>
+        <v>4.458</v>
       </c>
       <c r="V13" t="n">
         <v>4.7211</v>
       </c>
       <c r="W13" t="n">
-        <v>8.180900000000001</v>
+        <v>8.180899999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-3.4599</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6388</v>
+        <v>3.0305</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3367</v>
+        <v>1.7285</v>
       </c>
       <c r="F14" t="n">
         <v>1.3021</v>
@@ -1546,10 +1546,10 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1329</v>
+        <v>-0.7411</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2373</v>
+        <v>-0.8456</v>
       </c>
       <c r="U14" t="n">
         <v>0.1044</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2987</v>
+        <v>0.4207</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8546</v>
+        <v>1.0505</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.6298</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1885</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5504</v>
+        <v>-0.4284</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4501</v>
+        <v>-0.2543</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1002</v>
+        <v>-0.1741</v>
       </c>
       <c r="V15" t="n">
         <v>-0.63</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.408</v>
+        <v>-0.164</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5881</v>
+        <v>-1.1964</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1801</v>
+        <v>1.0324</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1031</v>
@@ -1702,13 +1702,13 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0461</v>
+        <v>-0.8021</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3132</v>
+        <v>-0.9214</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2671</v>
+        <v>0.1194</v>
       </c>
       <c r="V16" t="n">
         <v>0.6294</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.038</v>
+        <v>-1.0615</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.517</v>
+        <v>-0.7129</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5209</v>
+        <v>-0.3486</v>
       </c>
       <c r="G17" t="n">
         <v>0.0141</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4782</v>
+        <v>-0.5018</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.332</v>
+        <v>-0.5279</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1462</v>
+        <v>0.0261</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9444</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2895</v>
+        <v>-1.3504</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9048</v>
+        <v>0.6383</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1943</v>
+        <v>-1.9887</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4993</v>
+        <v>-1.0454</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0353</v>
+        <v>-2.5568</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.464</v>
+        <v>1.5114</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4989</v>
+        <v>0.7937</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5238</v>
+        <v>-0.5026</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0249</v>
+        <v>1.2963</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9982</v>
+        <v>-1.8391</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5591</v>
+        <v>-2.0543</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5609</v>
+        <v>0.2152</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0311</v>
+        <v>-0.3432</v>
       </c>
       <c r="T18" t="n">
-        <v>0.056</v>
+        <v>-0.1554</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0871</v>
+        <v>-0.1878</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.315</v>
+        <v>-1.2589</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5177</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3012</v>
+        <v>-1.754</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6383</v>
+        <v>0.3172</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9395</v>
+        <v>-2.0712</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0454</v>
+        <v>-1.4993</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5568</v>
+        <v>-1.0353</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5114</v>
+        <v>-0.464</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7937</v>
+        <v>0.4989</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5026</v>
+        <v>1.5238</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2963</v>
+        <v>-1.0249</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8391</v>
+        <v>-1.9982</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0543</v>
+        <v>-2.5591</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2152</v>
+        <v>0.5609</v>
       </c>
       <c r="P19" t="n">
-        <v>1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.294</v>
+        <v>-0.4955</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1554</v>
+        <v>-0.5316</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1385</v>
+        <v>0.036</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2589</v>
+        <v>-0.315</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2589</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6652</v>
+        <v>-1.959</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9302</v>
+        <v>-1.224</v>
       </c>
       <c r="F20" t="n">
         <v>-0.735</v>
@@ -2014,10 +2014,10 @@
         <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2189</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2561</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U20" t="n">
         <v>0.0373</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9532</v>
+        <v>-2.101</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8423</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1109</v>
+        <v>-1.2586</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3472</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5325</v>
+        <v>-0.6802</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2524</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2801</v>
+        <v>-0.4278</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6294</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0729</v>
+        <v>-3.196</v>
       </c>
       <c r="E22" t="n">
         <v>-1.6396</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4333</v>
+        <v>-1.5564</v>
       </c>
       <c r="G22" t="n">
         <v>-1.206</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2549</v>
+        <v>-0.378</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1977</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0572</v>
+        <v>-0.1803</v>
       </c>
       <c r="V22" t="n">
         <v>-0.315</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1627</v>
+        <v>-4.8185</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.102</v>
+        <v>-2.0041</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0607</v>
+        <v>-2.8145</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5577</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8083</v>
+        <v>-0.4641</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3196</v>
+        <v>-0.2216</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4887</v>
+        <v>-0.2425</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9439</v>
@@ -2287,7 +2287,7 @@
         <v>-3.8848</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.068299999999999</v>
+        <v>-9.068300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-6.5909</v>
@@ -2326,13 +2326,13 @@
         <v>14.8231</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.347300000000001</v>
+        <v>-5.347</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.457800000000001</v>
+        <v>-4.4578</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8892000000000001</v>
+        <v>-0.8893</v>
       </c>
       <c r="V24" t="n">
         <v>-4.7211</v>
